--- a/OKComputer_基金画像构建/基金产品画像_数据项清单.xlsx
+++ b/OKComputer_基金画像构建/基金产品画像_数据项清单.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -79,8 +79,13 @@
         <fgColor rgb="00F9F8F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E5CB3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -102,11 +107,55 @@
         <color rgb="00E4E0D8"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E4E0D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E0D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E4E0D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E0D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +175,12 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -500,6 +555,8 @@
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,6 +604,16 @@
           <t>呈现形式</t>
         </is>
       </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -554,11 +621,13 @@
           <t>页面顶部导航栏</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -589,6 +658,16 @@
           <t>H1标题(display-name)</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>产品名称取自产品注册全称。本产品为"建信纯债债券A"(530021)。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -619,6 +698,16 @@
           <t>标签(tag-pos)</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>生命周期状态标签: 正常运作=绿色状态点。状态由风控预警系统定期同步更新。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -649,6 +738,16 @@
           <t>标签(tag-brand)</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品分类标签库</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>资产大类=固收类。取自分类型标签库的一级分类。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -679,6 +778,16 @@
           <t>标签(tag-accent)</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>策略赛道=纯债/利率债。取自19赛道标签库的二级分类。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -709,6 +818,16 @@
           <t>标签(tag-pos)</t>
         </is>
       </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品梯队分类规则</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>产品梯队=旗舰产品。判定: 规模&gt;50亿→旗舰。建信纯债债券A规模59.62亿符合旗舰标准。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -739,6 +858,16 @@
           <t>标签(tag-warn)</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>关注标记=重点关注。判定逻辑: 综合规模/业绩/集中度/合规等维度触发。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -769,6 +898,16 @@
           <t>副标题文本</t>
         </is>
       </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>产品代码=530021(A类份额)。C类份额代码=531021。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -799,6 +938,16 @@
           <t>副标题文本</t>
         </is>
       </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品谱系血缘关系表</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>谱系路径=固收类 — 纯债/利率债。从产品谱系树中追溯大类→子类路径。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -829,6 +978,16 @@
           <t>页面右上角文本</t>
         </is>
       </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>系统配置信息 · 数据同步调度系统</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>数据更新时间=2026-07-17。估值数据T+1同步，季报/半年报在披露后2个工作日内更新。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -859,6 +1018,16 @@
           <t>页面右上角文本</t>
         </is>
       </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>系统配置信息 · 数据供应链管理</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>数据来源系统=产品主数据/估值系统/TA系统。页面右上角静态标注。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -866,11 +1035,13 @@
           <t>核心指标横带（两行）</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -901,6 +1072,16 @@
           <t>横带KPI(metric-ribbon)</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>最新总规模=59.62亿。取自估值系统2026年7月末资产净值。较上季变动=(59.62-上季净值)/上季净值=+1.82%。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -931,6 +1112,16 @@
           <t>横带KPI(metric-ribbon)</t>
         </is>
       </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>固收类规模占比=59.62/固收总规模501亿=11.9%。排名第8/68位=RANK(本产品规模, 固收类全部68只产品)。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -961,6 +1152,16 @@
           <t>横带KPI(metric-ribbon)</t>
         </is>
       </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>今年以来收益率=1.70%。计算: (最新净值-年初净值)/年初净值。同类排名前38%=PERCENTRANK(同类产品收益率, 本产品)。超额基准=-0.46%=1.70%-中债综合财富指数YTD。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -991,6 +1192,16 @@
           <t>横带KPI(metric-ribbon)</t>
         </is>
       </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书) · 风险评级模型</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>风险等级=R2中低风险。适配C2及以上投资者。依据招募说明书中的风险评级标准。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1021,6 +1232,16 @@
           <t>横带KPI(metric-ribbon)</t>
         </is>
       </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司内部财务系统 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>健康度评分=85分。多维度加权: 规模稳定性+业绩表现+盈利贡献+风控合规+渠道结构。评级=良好，纯债条线中上。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1051,6 +1272,16 @@
           <t>横带KPI(第二行)</t>
         </is>
       </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书) · 公司内部财务系统</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>年度管理费收入(预估)=1,789万元=SUM(日均规模×管理费率0.30%)。占固收条线12.5%=1,789/固收总管理费。全公司排名第5位。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1081,6 +1312,16 @@
           <t>横带KPI(第二行)</t>
         </is>
       </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>公司内部财务系统</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>产品利润率=62.5%=(管理费收入-运营成本)/管理费收入。投入产出比=1:2.68。同类中上水平。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1111,6 +1352,16 @@
           <t>横带KPI(第二行)</t>
         </is>
       </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>公司内部财务系统</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>单产品盈利贡献度=3.2%=本产品管理费/全公司总管理费收入。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1118,11 +1369,13 @@
           <t>Tab 1：基础概览</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1153,6 +1406,16 @@
           <t>折线图(可切换时间范围)</t>
         </is>
       </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · JS navData</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>净值走势(近1年/3年/5年/成立以来)。JS navData对象含4个时间维度的单位净值序列+业绩基准序列。x=时间标签, y=单位净值, yBenchmark=中债综合财富指数。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1183,6 +1446,16 @@
           <t>图表数据(Y轴)</t>
         </is>
       </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · JS navData</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>单位净值序列。近1年: 1.6592→1.6974(+2.3%)。近3年: 1.4452→1.6974(+17.5%)。近5年: 1.3669→1.6974(+24.2%)。成立以来: 1.0150→1.6974(+67.2%)。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1213,6 +1486,16 @@
           <t>图表辅助虚线</t>
         </is>
       </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · JS navData.yBenchmark</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>业绩基准=中债综合财富指数。近1年: 1.3580→1.4115(+3.9%)。仅非"全部"视图展示，用于衡量超额收益。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1243,6 +1526,16 @@
           <t>面积折线图(可切换时间范围)</t>
         </is>
       </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · JS scaleData</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>规模变动(可切换4个时间维度)。近1年: 52.35→59.62亿(+13.9%)。近3年: 38.25→59.62亿(+55.9%)。成立以来: 8.50→59.62亿(+601%)。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1273,6 +1566,16 @@
           <t>信息网格(info-grid)</t>
         </is>
       </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>基金全称=建信纯债债券型证券投资基金。法定全称，取自基金合同。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -1303,6 +1606,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>基金代码=530021(A类)。C类=531021。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1333,6 +1646,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>成立日期=2012-11-15。运作约13.7年，属于老牌产品。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1363,6 +1686,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>运作方式=开放式。每日开放申赎(非定开/非持有期)。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1393,6 +1726,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>基金管理人=建信基金管理有限责任公司。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1423,6 +1766,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>基金托管人=中国工商银行股份有限公司。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1453,6 +1806,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>现任基金经理=黎颖芳、彭紫云。双基金经理制，黎颖芳偏资产配置方向，彭紫云偏个券精选方向。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1483,6 +1846,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>彭紫云任职日期=2019-07-17，已管理本产品约7年。黎颖芳自2012-11-15成立日起管理，已约13.7年。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -1513,6 +1886,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>业绩比较基准=中债综合财富指数。为纯债基金通用基准。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1543,6 +1926,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>计价币种=人民币。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -1573,6 +1966,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>份额类别=A类/C类。A类=前端收费(530021)，C类=销售服务费(531021)。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1603,6 +2006,16 @@
           <t>信息网格</t>
         </is>
       </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>产品状态=正常开放申赎(绿色)。申赎状态由产品管理委员会审批，TA系统同步。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1610,11 +2023,13 @@
           <t>Tab 2：投资特征</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -1645,6 +2060,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>近1周收益率=0.04%=(最新净值-7日前净值)/7日前净值。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -1675,6 +2100,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>近1月收益率=0.12%。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1705,6 +2140,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>近3月收益率=0.59%。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -1735,6 +2180,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>近6月收益率=1.51%。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -1765,6 +2220,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>近1年收益率=1.83%。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -1795,6 +2260,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>近3年收益率=8.94%。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -1825,6 +2300,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>成立以来收益率=71.75%。累计收益=(最新净值-成立净值)/成立净值。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -1855,6 +2340,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名数据</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>同类排名分位=前38%=PERCENTRANK(同类纯债基金近1年收益, 本产品)。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -1885,6 +2380,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>年化波动率=1.21%=STDDEV(日收益率)×SQRT(250)。低于同类均值1.48%。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -1915,6 +2420,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>最大回撤=0.72%=MAX(1-当日净值/此前最高净值)。明显优于同类均值1.15%。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -1945,6 +2460,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>夏普比率=2.84=(年化收益-无风险利率)/年化波动率。高于同类均值1.92。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -1975,6 +2500,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>卡玛比率=4.75=年化收益/最大回撤。明显高于同类均值2.48。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -2005,6 +2540,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>组合久期=2.8年。灵活调整范围1.5-4.0年，当前为中性久期策略。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2035,6 +2580,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>杠杆率=115.3%=总资产/净资产。纯债基金杠杆上限为140%。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2065,6 +2620,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>下行风险=0.68%=STDDEV(MIN(日收益率,0))×SQRT(250)。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2095,6 +2660,16 @@
           <t>数据表格</t>
         </is>
       </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>索提诺比率=3.62=(年化收益-无风险利率)/下行风险。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -2125,6 +2700,16 @@
           <t>环形饼图</t>
         </is>
       </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>资产配置=债券92.6%+现金及等价物7.2%+其他0.2%。JS assetChart数据源。不参与股票投资。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2155,6 +2740,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>前5大重仓债券名称: 24国债05/23国开12/24工行二级资本债01/24华能集MTN003/23电网MTN006。全部AAA评级。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -2185,6 +2780,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>债券类型: 利率债/政策性金融债/银行二级资本债/中期票据/中期票据。覆盖利率+信用双维度。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -2215,6 +2820,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>占净值比: 8.76%/7.24%/5.68%/4.92%/4.35%。前5合计=31.0%，集中度合理。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -2245,6 +2860,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>债券评级: 全部AAA。高等级信用债为主，AAA占比92%。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -2275,6 +2900,16 @@
           <t>标签组(tag-muted)</t>
         </is>
       </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 投资策略说明</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>投资风格标签: 高等级信用债为主/久期中性策略/杠杆套息/不参与股票投资/AAA评级占比92%/行业分散配置。取自招募说明书+定期报告策略回顾。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2282,11 +2917,13 @@
           <t>Tab 3：运营规则</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -2894,11 +3531,13 @@
           <t>Tab 4：渠道客群</t>
         </is>
       </c>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -2929,6 +3568,16 @@
           <t>环形饼图</t>
         </is>
       </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>渠道保有规模: 银行153.56亿/直销52.01亿/券商27.25亿/第三方14.86亿。JS channelChart数据源。按销售商代码汇总保有净值。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -2959,6 +3608,16 @@
           <t>进度条</t>
         </is>
       </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水)</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>机构投资者占比=78.2%=机构持有净值/总净值。取自半年报持有人结构数据。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -2989,6 +3648,16 @@
           <t>进度条</t>
         </is>
       </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水)</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>个人投资者占比=21.8%=1-78.2%。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -3019,6 +3688,16 @@
           <t>统计卡片</t>
         </is>
       </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水)</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>总户数=12.86万户=COUNT(DISTINCT 基金账号)。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -3049,6 +3728,16 @@
           <t>统计卡片</t>
         </is>
       </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水)</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>户均持有规模=19.26万元=总规模/总户数。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -3079,6 +3768,16 @@
           <t>集中度卡片</t>
         </is>
       </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>最大单一持有人=和谐健康保险(9.12亿/15.3%)。取自2026年半年报前10大持有人披露。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -3109,6 +3808,16 @@
           <t>集中度卡片(阈值标注)</t>
         </is>
       </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 监管规定</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>单客户监管阈值=单客户≤20%(监管要求)。当前15.3%在合规范围内但偏高。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -3139,6 +3848,16 @@
           <t>集中度卡片(进度条)</t>
         </is>
       </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>前5大持有人合计=38.6%。集中度处于同类中等水平。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -3169,6 +3888,16 @@
           <t>集中度卡片(进度条)</t>
         </is>
       </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>前10大持有人合计=52.8%。机构主导型产品，前10大均为机构。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -3199,6 +3928,16 @@
           <t>行为卡片(进度条)</t>
         </is>
       </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 客户行为分析</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>平均持有期=186天。持有&gt;90天占比74.3%。债券型产品持有期普遍较长。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -3229,6 +3968,16 @@
           <t>行为卡片(进度条)</t>
         </is>
       </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 客户行为分析</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>客户复购率=42.5%。机构续约率78.2%，个人复购率35.1%。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -3259,6 +4008,16 @@
           <t>行为卡片(进度条)</t>
         </is>
       </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 客户行为分析</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>定投占比=3.2%。以机构大额申赎为主，零售定投渗透率低。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -3289,6 +4048,16 @@
           <t>表格(含机构类型标签)</t>
         </is>
       </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>前10大持有人名称: 和谐健康保险/兴业银行/中石油企业年金/中信证券/建信养老金/招商银行理财子/中国人寿养老/中船财务/建信信托/全国社保基金一零六组合。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -3319,6 +4088,16 @@
           <t>表格(彩色标签)</t>
         </is>
       </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 机构类型标签库</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>机构类型: 保险机构/商业银行/企业年金/证券公司/养老金/银行理财子/财务公司/信托计划/社保基金。持有人类型多元化。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -3349,6 +4128,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>持有规模: 9.12亿→1.25亿。第1名(15.3%)与第10名(2.1%)差距7.3倍。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -3379,6 +4168,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 产品半年报/季报</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>持有占比: 15.3%→2.1%。前10合计52.8%，剩余47.2%由约12.86万户分散持有。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -3409,6 +4208,16 @@
           <t>表格(红绿配色)</t>
         </is>
       </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 同比上期数据</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>较上期变动: +0.5pp/-1.2pp/+0.8pp/+1.5pp/+0.3pp/-0.4pp/新进/+0.2pp/-0.6pp/+0.1pp。兴业银行(-1.2pp)减持明显，中信证券(+1.5pp)增持最多，中国人寿养老为新进。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -3439,6 +4248,16 @@
           <t>渠道细分表格</t>
         </is>
       </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>银行渠道=36.96亿/62.0%。建行=23.67亿/39.7%。其他银行=13.29亿/22.3%。近1月变动+2.1%(银行合计)。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -3469,6 +4288,16 @@
           <t>渠道细分表格(缩进)</t>
         </is>
       </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>建行明细: 23.67亿/39.7%/+1.8%。核心渠道，贡献近四成规模。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -3499,6 +4328,16 @@
           <t>渠道细分表格(缩进)</t>
         </is>
       </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>其他银行明细: 13.29亿/22.3%/+2.6%。增速略高于建行渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -3529,6 +4368,16 @@
           <t>渠道细分表格</t>
         </is>
       </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>直销渠道: 12.52亿/21.0%/-0.8%。唯一负增长渠道，机构客户赎回影响。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -3559,6 +4408,16 @@
           <t>渠道细分表格</t>
         </is>
       </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>券商渠道: 6.56亿/11.0%/+3.5%。华泰/中信/国泰君安等12家券商。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -3589,6 +4448,16 @@
           <t>渠道细分表格</t>
         </is>
       </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>第三方互联网: 3.58亿/6.0%/+5.2%。增速最快渠道，互联网流量效应显著。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -3619,6 +4488,16 @@
           <t>标签组</t>
         </is>
       </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 客户标签引擎</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>客群标签: #机构主导型/#大额资金/#长期持有/#配置型需求/#低换手率/#集中度中等/#银行渠道依赖/#互联网渠道增长/#机构定投少。基于客户行为数据自动生成。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -3649,6 +4528,16 @@
           <t>callout-info卡片</t>
         </is>
       </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 客群分析模型</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>客群分析摘要: 6维度分析——机构主导(72%)/集中度风险(单客15.3%)/持有稳定性(186天)/渠道结构(建行39.7%)/互联网增长(+5.2%)/零售粘性(定投仅3.2%)。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -3679,6 +4568,16 @@
           <t>柱状图(申购/赎回/净申购)</t>
         </is>
       </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 每日申赎流水</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>近半年申购额(月度): JS redeemChart数据 [4.5,5.8,5.2,6.5,5.6,6.2]亿。月均约5.6亿。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -3709,6 +4608,16 @@
           <t>柱状图(申购/赎回/净申购)</t>
         </is>
       </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 每日申赎流水</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>近半年赎回额(月度): [3.8,4.2,4.1,4.8,4.6,5.0]亿。月均约4.4亿。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -3739,6 +4648,16 @@
           <t>折线图(申购/赎回/净申购)</t>
         </is>
       </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 每日申赎流水</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>近半年净申购=申购-赎回: [0.7,1.6,1.1,1.7,1.0,1.2]亿。连续6个月均为正净申购。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
@@ -3769,6 +4688,16 @@
           <t>详细表格</t>
         </is>
       </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(投资者账户/申赎流水)</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>货架上架明细: 7个货架(6个已上架+1个未上架)。建行手机银行/网银/天天基金/支付宝/券商/机构直销已上架；微信理财通未上架。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -3799,6 +4728,16 @@
           <t>表格列</t>
         </is>
       </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>上架日期: 2012-11-15(建行渠道，与产品成立日同步)→2019-08-12(支付宝，最晚上架)。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
@@ -3829,6 +4768,16 @@
           <t>表格列(状态标签)</t>
         </is>
       </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>上架状态: 6货架正常上架(绿色tag-pos)，微信理财通未上架(灰色tag-outline)。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -3859,6 +4808,16 @@
           <t>表格列(标签)</t>
         </is>
       </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · 产品管理委员会</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>是否主推: 建行手机银行=主推(tag-brand)。天天基金=次推(tag-warn)。其余=否。主推判定=渠道保有占比&gt;30%或战略重要性高。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
@@ -3889,6 +4848,16 @@
           <t>表格列</t>
         </is>
       </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · 产品费率表(招募说明书)</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>货架备注: 含费率优惠(建行申购优惠/天天1折)、推荐位(固收专区/纯债榜单)、渠道特性(PC端标准/支付宝仅A类/券商12家)等运营信息。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -3896,11 +4865,13 @@
           <t>Tab 5：经营分析</t>
         </is>
       </c>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="5" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="5" t="n"/>
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="11" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
@@ -4328,11 +5299,13 @@
           <t>Tab 6：竞争画像</t>
         </is>
       </c>
-      <c r="B134" s="5" t="n"/>
-      <c r="C134" s="5" t="n"/>
-      <c r="D134" s="5" t="n"/>
-      <c r="E134" s="5" t="n"/>
-      <c r="F134" s="5" t="n"/>
+      <c r="B134" s="10" t="n"/>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="10" t="n"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="11" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
@@ -4363,6 +5336,16 @@
           <t>雷达图(3条线)</t>
         </is>
       </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类产品对比 · JS competeRadarChart</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>竞争雷达图6维度: 收益率/夏普比率/回撤控制/规模优势/波动控制/费率性价比。本产品[73,70,80,75,78,65]→回撤控制最强(80)、费率性价比最弱(65)。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
@@ -4393,6 +5376,16 @@
           <t>对比表格(8行)</t>
         </is>
       </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>近1年收益: 本产品1.83%/同类均1.67%/TOP5均2.52%→排名前38%。低于TOP5约0.69pp。</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n">
@@ -4423,6 +5416,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>近3年收益: 8.94%/8.94%/12.85%→前44%。3年期与同类均值持平，无明显超额。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
@@ -4453,6 +5456,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>年化波动率: 1.05%/1.48%/0.95%→前30%。波动控制优于同类，接近TOP5水平。</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
@@ -4483,6 +5496,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>最大回撤: 0.85%/1.15%/0.45%→前32%。回撤控制良好，明显优于同类均值。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
@@ -4513,6 +5536,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>夏普比率: 1.74/1.92/3.25→前45%。略低于同类均值，主要受收益端拖累。</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
@@ -4543,6 +5576,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>管理费率: 0.30%/0.32%/0.15%→中等。TOP5低至0.15%，费率竞争压力较大。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
@@ -4573,6 +5616,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>规模排名: 59.62亿/28.5亿/452亿→前25%。规模优势明显，超过2倍同类均值。</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n">
@@ -4603,6 +5656,16 @@
           <t>对比表格</t>
         </is>
       </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类排名</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>卡玛比率: 2.15/2.48/5.20→前48%。收益回撤性价比略低于同类均值。</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
@@ -4633,6 +5696,16 @@
           <t>对比表格(6行)</t>
         </is>
       </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同赛道竞品筛选</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>同策略竞品: 易方达纯债(452亿/4.12%/1.35%)、南方通利(385亿/3.85%/1.42%)、广发纯债(362亿/3.58%/1.28%)、博时信用债(278亿/3.95%/1.52%)、工银纯债(215亿/3.28%/1.18%)。建信纯债规模第4、收益最低、波动最低。</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
@@ -4663,6 +5736,16 @@
           <t>横向对比条(contrast-row)</t>
         </is>
       </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · 内部产品对比</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>与建信稳定增利A对比: 规模(59.6 vs 82.4亿)、收益(1.83% vs 2.15%)、夏普(1.74 vs 1.95)、回撤(0.85% vs 1.15%)。增利A在收益端领先(含可转债增强)，纯债A在回撤控制端更优。</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -4693,6 +5776,16 @@
           <t>callout-pos卡片</t>
         </is>
       </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 竞争分析模型</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>竞争优势5条: 长期业绩稳定(13.7年累计71.75%)/波动率低于同类(1.05% vs 1.48%)/最大回撤优于同类(0.85% vs 1.15%)/双基金经理制(投研支持充分)/建信固收团队平台支撑。</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
@@ -4723,6 +5816,16 @@
           <t>callout-warn卡片</t>
         </is>
       </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 竞争分析模型</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>竞争短板4条: 近1年收益低于TOP5(1.83% vs 2.52%)/近3年收益与均值持平无明显超额/管理费率偏高(0.30% vs TOP5 0.15%)/夏普比率略低于均值(1.74 vs 1.92)。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
@@ -4753,6 +5856,16 @@
           <t>callout-info卡片</t>
         </is>
       </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 竞争分析模型 · 产品管理委员会</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>提升建议5条: 适度拉长久期→在利率下行周期提升收益弹性/增配中高等级信用债→增强票息/推出C类互联网专属费率优惠/打造"低波动纯债"品牌标签差异化/利用建行渠道优势提升零售渗透率。</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -4760,11 +5873,13 @@
           <t>Tab 7：基金经理画像</t>
         </is>
       </c>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="5" t="n"/>
-      <c r="E149" s="5" t="n"/>
-      <c r="F149" s="5" t="n"/>
+      <c r="B149" s="10" t="n"/>
+      <c r="C149" s="10" t="n"/>
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="10" t="n"/>
+      <c r="F149" s="10" t="n"/>
+      <c r="G149" s="10" t="n"/>
+      <c r="H149" s="11" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -4795,6 +5910,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>黎颖芳: 基金经理全名。2009年起任基金经理，任职超17年。</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
@@ -4825,6 +5950,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 基金经理标签库</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>角色标签: 资深基金经理·固收+投资专家·任职超17年。标签由HR系统+投资决策委员会评定。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
@@ -4855,6 +5990,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 中国证券投资基金业协会</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>证券从业年限=25.6年。自2000年大成基金起算。</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n">
@@ -4885,6 +6030,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>在管总规模=77亿=SUM(黎颖芳管理产品净值)。近年规模从216亿降至77亿，需关注是否涉及策略调整或产品清盘。</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
@@ -4915,6 +6070,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 产品-经理映射表</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>在管产品数=7只=COUNT(产品 WHERE 经理=黎颖芳)。</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n">
@@ -4945,6 +6110,16 @@
           <t>基金经理卡片-body卡片</t>
         </is>
       </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>基金经理年限=17.4年。自2009-02-19首次任基金经理起算。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
@@ -4975,6 +6150,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>年化回报: 该数据未在页面中单独展示。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
@@ -5005,6 +6190,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>任职本产品=2012-11-15至今(13.7年)。自产品成立日起管理，为原始基金经理。</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
@@ -5035,6 +6230,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>首次任基金经理=2009-02-19。任职首只产品距今17.4年。</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n">
@@ -5065,6 +6270,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>学历=硕士·湖南大学金融保险。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
@@ -5095,6 +6310,16 @@
           <t>基金经理卡片-代表产品</t>
         </is>
       </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>从业经历=大成基金(2000-2005)→建信基金(2005-至今)。建信司龄约21年。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
@@ -5125,6 +6350,16 @@
           <t>标签组</t>
         </is>
       </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>代表产品: 纯债债券A(任职回报+71.75%)/稳定得利A(+62.35%)/丰享债券A(2026.03新发)。任职回报=(最新净值-任职日净值)/任职日净值。</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
@@ -5155,6 +6390,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 投资风格评估</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>标签: #大类资产配置/#固收+投资专家/#保守配置型/#回撤控制优秀/#超17年老将/#资产轮动。由投研团队+风控定期评估。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n">
@@ -5185,6 +6430,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>彭紫云: 基金经理全名。2017年起任基金经理，任职超8年。</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
@@ -5215,6 +6470,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 基金经理标签库</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>角色标签: 基金经理·固收条线·任职超7年。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n">
@@ -5245,6 +6510,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 中国证券投资基金业协会</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>证券从业年限=13年。自2013年建信基金起算。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
@@ -5275,6 +6550,16 @@
           <t>基金经理卡片-header</t>
         </is>
       </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>在管总规模=175亿=SUM(彭紫云管理产品净值)。近年规模从120亿升至175亿，增长趋势良好。</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
@@ -5305,6 +6590,16 @@
           <t>基金经理卡片-body卡片</t>
         </is>
       </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 产品-经理映射表</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>在管产品数=18只=COUNT(产品 WHERE 经理=彭紫云)。管理产品数全公司最多，管理半径偏大需关注。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
@@ -5335,6 +6630,16 @@
           <t>基金经理卡片-body卡片</t>
         </is>
       </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>基金经理年限=8年。自2017-08-01首次任基金经理起算。</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n">
@@ -5365,6 +6670,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>年化回报=4.18%=GEOMEAN(管理产品的年化收益率)。</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n">
@@ -5395,6 +6710,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>任职本产品=2019-07-17至今(7.0年)。中途加入管理，与黎颖芳形成双经理制。</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n">
@@ -5425,6 +6750,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>首次任基金经理=2017-08-01。</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n">
@@ -5455,6 +6790,16 @@
           <t>基金经理卡片-管理经验</t>
         </is>
       </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>学历=硕士·经济学。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
@@ -5485,6 +6830,16 @@
           <t>基金经理卡片-代表产品</t>
         </is>
       </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>从业经历=建信基金(2013-至今)。建信司龄约13年。</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n">
@@ -5515,6 +6870,16 @@
           <t>标签组</t>
         </is>
       </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>代表产品: 纯债债券A(任职回报+26.47%)/短债债券A(+18.5%)/鑫悦90天(+9.2%)。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
@@ -5545,6 +6910,16 @@
           <t>详细表格</t>
         </is>
       </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 投资风格评估</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>标签: #久期中性策略/#高等级信用债/#回撤控制优先/#稳健派/#持有期产品专家。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n">
@@ -5575,6 +6950,16 @@
           <t>表格列</t>
         </is>
       </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 估值系统(TA系统)</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>在管产品一览(双经理合计7只): 纯债债券A(59.62亿·纯债·双经理)/稳定得利A(32.15亿·二级债基·黎颖芳)/短债债券A(58.60亿·短债·彭紫云)/鑫悦90天(42.30亿·中短债·彭紫云)/鑫福60天(36.20亿·中短债·彭紫云)/丰享债券A(9.51亿·二级债基·黎颖芳)/中短债增强A(15.80亿·中短债·彭紫云)。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n">
@@ -5605,6 +6990,16 @@
           <t>表格列(彩色标签)</t>
         </is>
       </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统)</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>在管产品规模: 59.62/32.15/58.60/42.30/36.20/9.51/15.80亿。彭紫云主管5只合计约162亿，黎颖芳主管3只(含双经理)合计约101亿。</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n">
@@ -5635,6 +7030,16 @@
           <t>表格列</t>
         </is>
       </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品分类标签</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>类型标签: 纯债(tag-accent)/二级债基(tag-warn)/短债(tag-pos)/中短债(tag-pos)。彭紫云以短债+中短债为主，黎颖芳以纯债+二级债为主。</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n">
@@ -5665,6 +7070,16 @@
           <t>表格列</t>
         </is>
       </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>主管经理: 黎颖芳(3只)/彭紫云(5只)/双经理(1只=本产品)。</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n">
@@ -5695,6 +7110,16 @@
           <t>折线图(3条线)</t>
         </is>
       </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>任职回报: +71.75%(黎颖芳·纯债)/+62.35%(黎颖芳·稳定得利)/+18.5%(彭紫云·短债)/+9.2%(彭紫云·鑫悦90天)/+7.5%(彭紫云·鑫福60天)/新发(黎颖芳·丰享)/+1.6%(彭紫云·中短债增强)。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n">
@@ -5725,6 +7150,16 @@
           <t>进度条评分</t>
         </is>
       </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · JS managerScaleChart</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>管理规模趋势: JS managerScaleChart数据。彭紫云120→175亿(↑45.8%)/黎颖芳185→77亿(↓58.4%)/本产品38→60亿(↑57.9%)。近3年13个季度数据点。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n">
@@ -5755,6 +7190,16 @@
           <t>进度条评分</t>
         </is>
       </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 投研团队评估</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>大类资产配置能力=90/100。黎颖芳17年经验覆盖多轮牛熊，擅长股债大类配置。</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n">
@@ -5785,6 +7230,16 @@
           <t>进度条评分</t>
         </is>
       </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 投研团队评估</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>久期管理能力=85/100。彭紫云久期中枢2.8年，灵活调整范围1.5-4.0年。</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n">
@@ -5815,6 +7270,16 @@
           <t>进度条评分</t>
         </is>
       </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 投研团队评估</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>回撤控制能力=92/100(最高)。双经理风控意识强，在管产品最大回撤均值低于同类。</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n">
@@ -5845,6 +7310,16 @@
           <t>callout-pos卡片</t>
         </is>
       </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 投研团队评估</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>团队协作度=88/100。黎颖芳(资产配置)+彭紫云(个券精选)，分工明确互补性强。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n">
@@ -5875,6 +7350,16 @@
           <t>callout-warn卡片</t>
         </is>
       </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>双基金经理制优势: 两人互补性强(配置+精选)，单一经理离职不会导致产品运作中断。接班安排: 彭紫云可承接黎颖芳职责。</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n">
@@ -5905,20 +7390,30 @@
           <t>callout-info表格</t>
         </is>
       </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>公司内部HR系统/基金经理信息库 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>需关注事项: 彭紫云管理18只产品管理半径偏大(人均5.4只的3.3倍)；黎颖芳规模从216亿降至77亿(降幅64%)，需关注是否涉及策略调整或产品清盘。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A119:F119"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A134:H134"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A119:H119"/>
+    <mergeCell ref="A149:H149"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5930,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5938,6 +7433,8 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5947,6 +7444,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5971,6 +7469,16 @@
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -5998,6 +7506,16 @@
           <t>固收类中排名第8/68位</t>
         </is>
       </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>最新总规模=59.62亿元。取自估值系统2026年7月末资产净值。较上季变动=(59.62-上季净值)/上季净值=+1.82%。固收类中排名=RANK(本产品,固收类68只产品)=第8位。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -6023,6 +7541,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>固收类规模占比=59.62/固收总规模501亿=11.9%。固收类总规模=SUM(固收类全部产品净值)。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -6048,6 +7576,16 @@
           <t>超额基准-0.46%</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>今年以来收益率=1.70%=(最新净值-年初净值)/年初净值。同类排名前38%=PERCENTRANK(同类纯债基金YTD收益,本产品)。超额基准=-0.46%=1.70%-中债综合财富指数YTD。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -6073,6 +7611,16 @@
           <t>适配C2及以上投资者</t>
         </is>
       </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书) · 风险评级模型</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>风险等级=R2中低风险。依据招募说明书风险评级，适配C2及以上风险承受等级投资者。判定逻辑: 纯债基金(不投股票)+久期≤3年→R2。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -6098,6 +7646,16 @@
           <t>纯债条线中上</t>
         </is>
       </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 内部财务系统 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>健康度评分=85分。多维度加权评分: 规模稳定性(权重25%)+业绩表现(25%)+盈利贡献(20%)+风控合规(20%)+渠道结构(10%)。评级=良好(80-89分区间)，纯债条线中上。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -6123,6 +7681,16 @@
           <t>占固收条线12.5%</t>
         </is>
       </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书) · 内部财务系统</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>年度管理费收入(预估)=1,789万元=SUM(日均规模)×管理费率0.30%。占固收条线12.5%=1,789/固收总管理费14,312万。全公司排名第5位。YTD已实现895.32万，预计全年1,789万。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -6148,6 +7716,16 @@
           <t>投入产出比1:2.68</t>
         </is>
       </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>内部财务系统</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>产品利润率=62.5%=(管理费收入-运营成本)/管理费收入。运营成本含投研人力/系统/合规/托管等分摊。投入产出比=管理费收入/运营成本=1:2.68。固收条线排名第5位。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -6173,6 +7751,16 @@
           <t>管理费占全公司总营收比重</t>
         </is>
       </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>内部财务系统</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>单产品盈利贡献度=3.2%=本产品管理费1,789万/全公司总管理费收入(约5.59亿)。注: 全公司总管理费收入为估算值，基于管理规模×加权平均费率。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -6198,6 +7786,16 @@
           <t>预计全年1,789万元</t>
         </is>
       </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>内部财务系统</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>本年度管理费收入(YTD)=895.32万元=SUM(2026.01.01至今的日均规模×管理费率0.30%÷365×已过天数)。预计全年=YTD/已过天数×365≈1,789万元。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -6223,6 +7821,16 @@
           <t>尾佣占比26.6%</t>
         </is>
       </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>内部财务系统 · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>尾佣收入(YTD)=238.56万元。尾佣占比=238.56/895.32=26.6%。尾佣=支付给销售渠道的管理费分成(通常为管理费的20-40%)。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6248,6 +7856,16 @@
           <t>运作约13.7年</t>
         </is>
       </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>成立日期=2012-11-15。基金合同生效日。截至2026年7月已运作约13.7年。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -6273,6 +7891,16 @@
           <t>A类/C类 530021/531021</t>
         </is>
       </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>基金代码=530021(A类份额)。C类份额代码=531021。A类前端收费(申购时支付)，C类免申购费但收销售服务费。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6298,6 +7926,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书)</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>业绩比较基准=中债综合财富指数。纯债基金的通用基准，反映中国债券市场整体走势。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -6323,6 +7961,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>基金管理人=建信基金管理有限责任公司。中国建设银行持股65%，为银行系公募基金公司。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6348,10 +7996,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>基金托管人=中国工商银行股份有限公司。托管人负责基金资产保管和清算交收。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6363,7 +8022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6371,6 +8030,8 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6380,16 +8041,19 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>核心业绩指标</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -6415,6 +8079,16 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -6442,6 +8116,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>近1周收益率=0.04%=(最新单位净值-7日前净值)/7日前净值。不设同类排名，短期波动参考价值有限。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -6467,6 +8151,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>近1月收益率=0.12%。纯债基金月度收益波动小(正常范围0-0.5%)。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -6492,6 +8186,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>近3月收益率=0.59%。季度维度可初步反映久期策略和票息收益的综合效果。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -6517,6 +8221,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>近6月收益率=1.51%。半年度维度可较好衡量基金经理的中期业绩表现。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -6542,6 +8256,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · 同类排名数据</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>近1年收益率=1.83%=(最新净值-12月前净值)/12月前净值。同类排名=PERCENTRANK(同类纯债基金近1年收益率,1.83%)=前38%。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -6567,6 +8291,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · 同类排名数据</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>近3年收益率=8.94%=(最新净值-3年前净值)/3年前净值。同类排名=前44%。与同类均值持平，无明显超额收益。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -6592,6 +8326,16 @@
           <t>2012年成立，约13.7年</t>
         </is>
       </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>成立以来收益率=71.75%=(最新净值-成立净值1.0000)/1.0000。成立13.7年累计回报，年化约4.0%。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -6599,10 +8343,12 @@
           <t>风险收益指标</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -6628,6 +8374,16 @@
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -6655,6 +8411,16 @@
           <t>低于同类均值</t>
         </is>
       </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>年化波动率=1.21%=STDDEV(日收益率)×SQRT(250)。同类均值=1.48%。低于同类均值→波动控制良好。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6680,6 +8446,16 @@
           <t>明显优于同类均值</t>
         </is>
       </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>最大回撤=0.72%=MAX(1-当日净值/此前最高净值)。同类均值=1.15%。明显优于同类→下行保护能力强。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -6705,6 +8481,16 @@
           <t>高于同类均值</t>
         </is>
       </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>夏普比率=2.84=(年化收益-无风险利率)/年化波动率。无风险利率取1年期国债收益率。同类均值=1.92。高于同类→风险调整后收益优秀。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6730,6 +8516,16 @@
           <t>明显高于同类均值</t>
         </is>
       </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>卡玛比率=4.75=年化收益/最大回撤。同类均值=2.48。明显高于同类→单位回撤带来的收益回报高。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -6755,6 +8551,16 @@
           <t>灵活调整范围1.5-4.0年</t>
         </is>
       </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>组合久期=2.8年=SUM(债券久期×占比)。灵活调整范围1.5-4.0年。当前中性偏短，反映稳健操作风格。久期越长→对利率变动越敏感。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -6780,6 +8586,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>杠杆率=115.3%=总资产/净资产。纯债基金杠杆上限140%。当前杠杆适中，通过回购融资增厚收益。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -6805,6 +8621,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>下行风险=0.68%=STDDEV(MIN(日收益率,0))×SQRT(250)。仅衡量负收益波动，比普通波动率更能反映真实风险。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -6830,6 +8656,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>索提诺比率=3.62=(年化收益-无风险利率)/下行风险。使用下行风险替代总波动率，更精准衡量下行风险调整后收益。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -6837,10 +8673,12 @@
           <t>前五大重仓债券</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -6866,6 +8704,16 @@
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>评级</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -6893,6 +8741,16 @@
           <t>AAA</t>
         </is>
       </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>24国债05: 占净值比=8.76%=持仓市值/基金净资产。利率债→无信用风险，由国家信用背书。评级=AAA。为第一大重仓。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -6918,6 +8776,16 @@
           <t>AAA</t>
         </is>
       </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>23国开12: 7.24%。政策性金融债→准主权信用，由国家开发银行发行。评级=AAA。流动性好。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -6943,6 +8811,16 @@
           <t>AAA</t>
         </is>
       </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>24工行二级资本债01: 5.68%。银行二级资本债→商业银行发行的次级债券，票息高于同期限利率债。评级=AAA。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -6968,6 +8846,16 @@
           <t>AAA</t>
         </is>
       </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>24华能集MTN003: 4.92%。中期票据→华能集团(AAA央企)发行的3年期MTN。信用风险极低，票息适中。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -6993,13 +8881,24 @@
           <t>AAA</t>
         </is>
       </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · 2026年半年报</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>23电网MTN006: 4.35%。中期票据→国家电网(AAA央企)发行。前5大合计=8.76+7.24+5.68+4.92+4.35=30.95%。集中度合理，单一债券均&lt;10%。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="5">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7011,7 +8910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7019,6 +8918,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7028,16 +8929,19 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>渠道保有规模分布</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -7065,6 +8969,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7090,6 +9004,16 @@
           <t>最大渠道</t>
         </is>
       </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>银行渠道合计=36.96亿=建行23.67+其他银行13.29。占比=36.96/59.62=62.0%。近1月变动+2.1%=(本月末-上月末)/上月末。最大渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7115,6 +9039,16 @@
           <t>核心渠道</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>建设银行=23.67亿。占比=23.67/59.62=39.7%。近1月+1.8%。核心渠道，贡献近四成规模，母行协同优势显著。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7140,6 +9074,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>其他银行=13.29亿=银行合计36.96-建行23.67。占比22.3%。近1月+2.6%，增速略高于建行渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -7165,6 +9109,16 @@
           <t>机构直销为主</t>
         </is>
       </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>直销渠道=12.52亿。占比21.0%。近1月-0.8%(唯一负增长)。以机构直销为主，费率单独协商。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7190,6 +9144,16 @@
           <t>华泰/中信/国泰君安等12家</t>
         </is>
       </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>券商渠道=6.56亿。占比11.0%。近1月+3.5%。覆盖华泰/中信/国泰君安等12家券商。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -7215,6 +9179,16 @@
           <t>增速最快渠道</t>
         </is>
       </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>第三方互联网=3.58亿。占比6.0%。近1月+5.2%(增速最快)。互联网流量效应显著。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -7222,10 +9196,12 @@
           <t>前10大持有人明细</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -7253,6 +9229,16 @@
           <t>较上期变动</t>
         </is>
       </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -7278,6 +9264,16 @@
           <t>+0.5pp</t>
         </is>
       </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>和谐健康保险: 9.12亿/15.3%。较上期+0.5pp(增持)。最大单一持有人，保险机构→配置型需求。趋近监管阈值(20%)需关注。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7303,6 +9299,16 @@
           <t>-1.2pp</t>
         </is>
       </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>兴业银行: 5.36亿/9.0%。较上期-1.2pp(减持)。商业银行自营资金→受银行流动性管理影响较大。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -7328,6 +9334,16 @@
           <t>+0.8pp</t>
         </is>
       </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>中石油企业年金: 3.88亿/6.5%。较上期+0.8pp。企业年金→长期配置型资金，持有稳定性高。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7353,6 +9369,16 @@
           <t>+1.5pp</t>
         </is>
       </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>中信证券: 2.68亿/4.5%。较上期+1.5pp(增持最多)。证券公司→交易型资金，变动幅度大。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -7378,6 +9404,16 @@
           <t>+0.3pp</t>
         </is>
       </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>建信养老金管理: 1.97亿/3.3%。较上期+0.3pp。养老金→关联方(建信体系内)，长期战略合作。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7403,6 +9439,16 @@
           <t>-0.4pp</t>
         </is>
       </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>招商银行理财: 2.33亿/3.9%。较上期-0.4pp。银行理财子→受理财规模管控和净值化转型影响。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -7428,6 +9474,16 @@
           <t>新进</t>
         </is>
       </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>中国人寿养老: 1.91亿/3.2%。较上期=新进。保险机构新增→反映对纯债策略的认可。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7453,6 +9509,16 @@
           <t>+0.2pp</t>
         </is>
       </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>中船财务: 1.67亿/2.8%。较上期+0.2pp。财务公司→央企内部资金管理需求。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -7478,6 +9544,16 @@
           <t>-0.6pp</t>
         </is>
       </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>建信信托·固收优选: 1.31亿/2.2%。较上期-0.6pp。信托计划→关联方，受信托行业监管趋严影响。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7503,20 +9579,41 @@
           <t>+0.1pp</t>
         </is>
       </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 2026年半年报持有人披露 · Wind终端</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>全国社保基金一零六: 1.25亿/2.1%。较上期+0.1pp。社保基金→国家战略配置，最高信用等级持有人。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>前10大持有人合计占比：52.8% | 机构投资者78.2% · 个人投资者21.8% | 数据截止2026-06-30</t>
         </is>
       </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户/申赎流水) · 产品半年报/季报 · 派生计算</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>前10大合计=15.3+9.0+6.5+4.5+3.3+3.9+3.2+2.8+2.2+2.1=52.8%。机构投资者78.2%=机构持有净值/总净值。个人投资者21.8%=1-78.2%。数据截止2026-06-30。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7528,13 +9625,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7544,15 +9643,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>基金经理基本信息对比</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -7575,6 +9677,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7597,6 +9709,16 @@
           <t>双经理制</t>
         </is>
       </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库 · 基金经理标签库 · 投资决策委员会评定</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>角色定位: 黎颖芳=资深基金经理·固收+投资专家(2009年起任职，超17年)。彭紫云=基金经理·固收条线(2017年起任职，超8年)。双经理制→大类配置+个券精选分工。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7619,6 +9741,16 @@
           <t>黎颖芳经验更丰富</t>
         </is>
       </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库 · 基金业协会从业人员公示</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>证券从业年限: 黎颖芳=25.6年(自2000年大成基金起算)。彭紫云=13年(自2013年建信基金起算)。计算=当前日期-首次证券从业日期。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7641,6 +9773,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库 · 基金业协会从业人员公示</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>基金经理年限: 黎颖芳=17.4年(自2009-02-19首次任基金经理起算)。彭紫云=8年(自2017-08-01起算)。年限=当前日期-首次任基金经理日期。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -7663,6 +9805,16 @@
           <t>彭紫云管理规模更大</t>
         </is>
       </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · 产品-经理映射表</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>在管总规模: 黎颖芳=77亿=SUM(黎颖芳管理产品净值)。彭紫云=175亿=SUM(彭紫云管理产品净值)。近年趋势: 黎颖芳从216亿降至77亿(↓64%)，彭紫云从120亿升至175亿(↑46%)。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7685,6 +9837,16 @@
           <t>彭紫云管理半径更大</t>
         </is>
       </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库 · 产品-经理映射表</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>在管产品数: 黎颖芳=7只=COUNT(产品 WHERE 经理=黎颖芳)。彭紫云=18只=COUNT(产品 WHERE 经理=彭紫云)。彭紫云为全公司管理产品数最多的经理，管理半径偏大。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -7707,6 +9869,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>年化回报: 彭紫云=4.18%=GEOMEAN(管理产品的年化收益率)。黎颖芳该数据未在页面中单独展示。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7729,6 +9901,16 @@
           <t>黎颖芳从成立即管理</t>
         </is>
       </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>任职本产品: 黎颖芳=2012-11-15至今(13.7年)，自产品成立日起管理。彭紫云=2019-07-17至今(7.0年)，中途加入。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7751,6 +9933,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>首次任基金经理: 黎颖芳=2009-02-19。彭紫云=2017-08-01。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7773,6 +9965,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>学历: 黎颖芳=硕士·湖南大学金融保险。彭紫云=硕士·经济学。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -7795,6 +9997,16 @@
           <t>黎颖芳建信司龄20年</t>
         </is>
       </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>从业经历: 黎颖芳=大成基金(2000-2005)→建信基金(2005-至今)，建信司龄约21年。彭紫云=建信基金(2013-至今)，司龄约13年。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7817,6 +10029,16 @@
           <t>均属长期稳定</t>
         </is>
       </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>建信基金司龄: 黎颖芳=20年(2005年入职)。彭紫云=13年(2013年入职)。均属长期稳定员工，离职风险低。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -7839,6 +10061,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>风控预警系统 · 证监会/基金业协会处罚记录</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>近3年监管处罚: 黎颖芳=无。彭紫云=无。查询来源: 证监会行政处罚公示+基金业协会自律处分记录。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7861,6 +10093,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>风控预警系统 · HR</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>离职风险评估: 黎颖芳=低(超20年老员工，与公司深度绑定)。彭紫云=低(核心投研骨干，在建信体系内成长)。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -7883,6 +10125,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>公司HR系统/基金经理信息库 · 投资决策委员会</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>接班安排: 黎颖芳→彭紫云可承接(因已共同管理7年)。彭紫云→团队储备充足(固收条线有多名资深经理)。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7890,9 +10142,11 @@
           <t>在管产品一览（双经理合计）</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -7915,6 +10169,16 @@
           <t>主管经理</t>
         </is>
       </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -7935,6 +10199,16 @@
           <t>黎颖芳/彭紫云</t>
         </is>
       </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>建信纯债债券A(530021): 59.62亿·纯债·双经理。⬅本产品(蓝色高亮)。双经理=黎颖芳(资产配置)+彭紫云(个券精选)。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7955,6 +10229,16 @@
           <t>黎颖芳</t>
         </is>
       </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>建信稳定得利债券A(000875): 32.15亿·二级债基·黎颖芳。含可转债/权益增强仓位，属于固收+策略。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -7975,6 +10259,16 @@
           <t>彭紫云</t>
         </is>
       </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>建信短债债券A(006581): 58.60亿·短债·彭紫云。中短债赛道龙头产品，互联网渠道渗透率高。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -7995,6 +10289,16 @@
           <t>彭紫云</t>
         </is>
       </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>建信鑫悦90天滚动持有(014855): 42.30亿·中短债·彭紫云。滚动持有期设计，90天锁定期锁定客户资金。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -8015,6 +10319,16 @@
           <t>彭紫云</t>
         </is>
       </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>建信鑫福60天持有期(016035): 36.20亿·中短债·彭紫云。60天持有期，流动性介于30天与90天之间。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -8035,6 +10349,16 @@
           <t>黎颖芳</t>
         </is>
       </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>建信丰享债券A(026506): 9.51亿·二级债基·黎颖芳。2026年3月新发，尚在规模爬坡期。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -8055,6 +10379,16 @@
           <t>彭紫云</t>
         </is>
       </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 公司HR系统/基金经理信息库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>建信中短债增强债券A(022443): 15.80亿·中短债·彭紫云。2026年2月新发，规模增长较快(15.8亿)。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -8062,9 +10396,11 @@
           <t>投资风格画像评分（团队综合）</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -8087,6 +10423,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -8107,6 +10453,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>投研团队评估 · 投资决策委员会评定</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>大类资产配置能力=90/100。黎颖芳17年经验覆盖多轮牛熊周期(2009-2026)，擅长股债大类配置。评分依据: 历史配置准确率+风险调整后收益+同类排名。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -8127,6 +10483,16 @@
           <t>彭紫云主导</t>
         </is>
       </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>投研团队评估 · 投资决策委员会评定</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>久期管理能力=85/100。彭紫云久期中枢2.8年，灵活调整范围1.5-4.0年。评分依据: 久期调整及时性+利率趋势判断准确率+久期调整带来的超额收益。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -8147,6 +10513,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>投研团队评估 · 投资决策委员会评定</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>回撤控制能力=92/100(四项中最高)。双经理风控意识强，在管产品最大回撤均值(0.72%)低于同类均值(1.15%)。评分依据: 最大回撤绝对值+回撤修复速度+尾部风险控制。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -8167,13 +10543,24 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>投研团队评估 · 投资决策委员会评定</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>团队协作度=88/100。黎颖芳(资产配置方向)+彭紫云(个券精选方向)，分工明确互补性强。评分依据: 双经理共管产品(本产品)的业绩一致性+策略沟通频率+决策效率。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A30:D30"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
